--- a/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,01</t>
+          <t>-4,84; 1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,53</t>
+          <t>-1,34; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,21</t>
+          <t>-3,72; 9,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,27</t>
+          <t>-100,0; 107,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 330,2</t>
+          <t>-52,78; 343,29</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,46</t>
+          <t>-3,64; 2,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,67</t>
+          <t>-3,42; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,86</t>
+          <t>-4,04; 3,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,18</t>
+          <t>-5,13; 4,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 75,54</t>
+          <t>-56,14; 62,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 103,64</t>
+          <t>-48,55; 98,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 70,2</t>
+          <t>-54,85; 67,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 75,7</t>
+          <t>-49,2; 76,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 10,19</t>
+          <t>-2,65; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,74</t>
+          <t>-5,72; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 6,7</t>
+          <t>-4,4; 6,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 0,53</t>
+          <t>-11,49; 0,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 158,85</t>
+          <t>-25,15; 152,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 62,55</t>
+          <t>-39,0; 68,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 73,68</t>
+          <t>-29,43; 77,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 7,97</t>
+          <t>-59,89; 7,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 12,09</t>
+          <t>-1,63; 12,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 6,73</t>
+          <t>-8,24; 5,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 5,03</t>
+          <t>-7,89; 5,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,86</t>
+          <t>-6,47; 3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 68,38</t>
+          <t>-6,92; 70,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 33,02</t>
+          <t>-29,6; 27,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 35,11</t>
+          <t>-38,89; 40,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 34,41</t>
+          <t>-47,42; 38,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,05</t>
+          <t>-0,54; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,11</t>
+          <t>-3,31; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,38</t>
+          <t>-2,4; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,84</t>
+          <t>-4,7; 0,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 59,8</t>
+          <t>-4,87; 56,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 22,23</t>
+          <t>-27,02; 22,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 29,0</t>
+          <t>-23,71; 31,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 8,52</t>
+          <t>-38,63; 8,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,0</t>
+          <t>-5,25; 0,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,43</t>
+          <t>-1,25; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 9,81</t>
+          <t>-3,79; 8,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,83</t>
+          <t>-92,26; 118,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 343,29</t>
+          <t>-50,45; 313,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,28</t>
+          <t>-3,5; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,38</t>
+          <t>-3,13; 3,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,12</t>
+          <t>-4,04; 2,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,35</t>
+          <t>-5,01; 4,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,14; 62,91</t>
+          <t>-51,92; 63,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 98,59</t>
+          <t>-46,8; 102,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 67,64</t>
+          <t>-48,31; 68,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 76,25</t>
+          <t>-48,02; 69,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 9,19</t>
+          <t>-2,65; 8,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,39</t>
+          <t>-6,25; 5,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,86</t>
+          <t>-4,66; 6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 0,93</t>
+          <t>-10,8; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 152,44</t>
+          <t>-24,22; 142,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 68,74</t>
+          <t>-41,09; 67,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 77,54</t>
+          <t>-32,2; 74,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 7,37</t>
+          <t>-57,85; 14,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,16</t>
+          <t>-1,21; 12,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 5,82</t>
+          <t>-8,8; 6,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 5,11</t>
+          <t>-7,23; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,21</t>
+          <t>-6,04; 3,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 70,65</t>
+          <t>-5,39; 70,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 27,36</t>
+          <t>-32,12; 31,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 40,25</t>
+          <t>-38,36; 39,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 38,41</t>
+          <t>-49,73; 34,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,62</t>
+          <t>-0,57; 4,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,04</t>
+          <t>-3,2; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,56</t>
+          <t>-2,4; 2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,82</t>
+          <t>-4,9; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 56,73</t>
+          <t>-5,53; 56,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 22,26</t>
+          <t>-26,11; 21,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 31,76</t>
+          <t>-23,06; 35,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 8,11</t>
+          <t>-39,27; 9,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,88</t>
+          <t>-5,19; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,2</t>
+          <t>-1,21; 3,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 8,65</t>
+          <t>-2,22; 9,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,26; 118,04</t>
+          <t>-100,0; 153,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,45; 313,58</t>
+          <t>-42,48; 373,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-6,05%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,3</t>
+          <t>-3,6; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,57</t>
+          <t>-3,09; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,95</t>
+          <t>-4,15; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 4,18</t>
+          <t>-4,53; 5,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 63,22</t>
+          <t>-52,71; 75,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 102,23</t>
+          <t>-48,0; 103,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 68,46</t>
+          <t>-52,28; 70,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 69,84</t>
+          <t>-44,17; 89,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>-5,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,51%</t>
+          <t>-34,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,71</t>
+          <t>-2,28; 10,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 5,99</t>
+          <t>-5,96; 5,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 6,87</t>
+          <t>-4,74; 6,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 1,28</t>
+          <t>-12,2; 0,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 142,42</t>
+          <t>-22,15; 158,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 67,87</t>
+          <t>-40,23; 62,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 74,48</t>
+          <t>-30,48; 73,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 14,78</t>
+          <t>-60,71; 3,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,45%</t>
+          <t>-4,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 12,66</t>
+          <t>-1,43; 12,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,56</t>
+          <t>-8,88; 6,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,05</t>
+          <t>-8,25; 5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 3,02</t>
+          <t>-5,47; 3,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 70,53</t>
+          <t>-5,53; 68,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 31,18</t>
+          <t>-32,1; 33,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 39,02</t>
+          <t>-40,5; 35,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 34,07</t>
+          <t>-41,52; 43,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-14,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,71</t>
+          <t>-0,24; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,0</t>
+          <t>-2,94; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,81</t>
+          <t>-2,42; 2,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,88</t>
+          <t>-4,57; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 56,3</t>
+          <t>-2,57; 59,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 21,34</t>
+          <t>-24,57; 22,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 35,39</t>
+          <t>-23,05; 29,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 9,51</t>
+          <t>-34,55; 11,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-56,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>148,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53,43%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.167515007318185</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.88034507205372</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.11241185475081</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.484935144132541</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.5672940536524433</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.481165690983988</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.5342811507955383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,19; 1,01</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,21; 3,53</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 9,53</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 153,27</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-42,48; 373,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.188310400223204</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.210101582385649</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.215274084773507</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.4248245918564503</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.981981570452763</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.007346364601746</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.527328641948142</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.52565213840758</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>1.532657447055371</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>3.731427478513863</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,6; 2,46</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 3,67</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 2,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,53; 5,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,71; 75,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-48,0; 103,64</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-52,28; 70,2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-44,17; 89,04</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5753415956885527</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1585967809016868</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6695222593739953</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.2186569978042396</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1116149091725193</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.03010697901082438</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1077014875627502</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.02644616572506995</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-34,68%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.595791826795576</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.085156034254497</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.14826542403925</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.532162601622325</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5270837594239223</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4800207122845746</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.522754438227117</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4417133797471668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 10,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,96; 5,74</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,74; 6,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-12,2; 0,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-22,15; 158,85</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-40,23; 62,55</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-30,48; 73,68</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-60,71; 3,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.460410824448395</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.674944852106615</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.859337481367157</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.16021952873691</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.755420230994408</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.036421959463782</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7020151932129796</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.8903746767138941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +813,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-4,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.32285411722571</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1068071488541364</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.179061823539332</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.517853202833735</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3760610717271498</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.008811099182661489</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.0991054818393301</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3467944599591034</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 12,09</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,88; 6,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 5,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,47; 3,8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,53; 68,38</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-32,1; 33,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-40,5; 35,11</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-41,52; 43,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.282115114832796</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.960246384467328</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.742072898581049</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.19975240167392</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2215315320510421</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4023195577903151</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3047526106022851</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6070731888736294</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.18649403661434</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.73662070002926</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.69509990752468</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.1594574436642024</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.588544289443546</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6255084032460365</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.7368114622467185</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.03240070841638378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.417818711425867</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.077097288543352</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.332259925267576</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.5057461316063577</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2624218556110965</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0442046921433721</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.07887707648741384</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.04637319482620361</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.427456621949321</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.88100490819639</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.252416124428962</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.472190235383886</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.05527160481132998</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3210171210633553</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4049575484646985</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4152372240715646</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>12.08678801103514</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.730934620271259</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.027317735519453</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.800239628155579</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.683755866480676</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3302316394277716</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3510515747721512</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4324548313157244</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-14,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 5,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,94; 2,11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 2,38</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 1,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 59,8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-24,57; 22,23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-23,05; 29,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-34,55; 11,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.18668960023648</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5043199453750785</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1082508893619716</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.610942901591542</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.231788628049038</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.04622175169089576</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01164537794615412</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1426292529669791</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.2363277152559292</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.9361848507163</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.422760957011231</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.566567269393126</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.0256771119128923</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2457016873010037</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2304963226366993</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3455460429331322</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.048634675393853</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.111667331910583</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.376382194216286</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.057913882672275</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5979666051858641</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2222727458325775</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2899793846663513</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1125027260278271</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1111,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
